--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY282"/>
+  <dimension ref="A1:AZ282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110471482</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100447568</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91171463</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91171484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1310,6 +1340,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781486</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1411,6 +1446,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91171608</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102873</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,6 +1679,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744753</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94744778</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110687446</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135386753</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2087,6 +2152,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101070100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124946575</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2303,6 +2378,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102184538</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118000431</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2532,6 +2617,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105939</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2633,6 +2723,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811897</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2739,6 +2834,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91171545</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2845,6 +2945,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781631</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2951,6 +3056,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075745</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3057,6 +3167,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075954</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3163,6 +3278,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076280</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076285</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3365,6 +3490,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076287</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3471,6 +3601,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076294</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3572,6 +3707,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076300</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3673,6 +3813,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105906</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3774,6 +3919,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105927</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3880,6 +4030,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105950</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3986,6 +4141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076102</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4087,6 +4247,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812059</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4188,6 +4353,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91784813</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4294,6 +4464,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076217</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4400,6 +4575,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105921</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4501,6 +4681,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812086</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4602,6 +4787,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812095</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4716,6 +4906,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122279529</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4821,6 +5016,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105899</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4926,6 +5126,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131560800</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5028,6 +5233,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100447743</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5135,6 +5345,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833619</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5245,6 +5460,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100447685</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5351,6 +5571,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91171492</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5452,6 +5677,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879416</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5553,6 +5783,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075105</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5659,6 +5894,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075131</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5765,6 +6005,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075154</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5866,6 +6111,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075156</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5967,6 +6217,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075325</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6073,6 +6328,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075343</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6179,6 +6439,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075355</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6285,6 +6550,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075361</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6386,6 +6656,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075371</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6492,6 +6767,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075392</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6598,6 +6878,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075405</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6699,6 +6984,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075443</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6805,6 +7095,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075456</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6911,6 +7206,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075572</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7012,6 +7312,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811767</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7113,6 +7418,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812352</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7214,6 +7524,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811845</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7315,6 +7630,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811671</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7416,6 +7736,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794430</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7517,6 +7842,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811626</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7618,6 +7948,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811794</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7723,6 +8058,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88737836</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7824,6 +8164,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811630</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7925,6 +8270,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811748</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8026,6 +8376,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811861</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8127,6 +8482,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794413</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8228,6 +8588,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794443</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8329,6 +8694,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811622</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8430,6 +8800,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811687</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8531,6 +8906,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811877</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8632,6 +9012,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95572753</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8737,6 +9122,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122279509</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8842,6 +9232,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838880</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8947,6 +9342,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075250</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9054,6 +9454,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075425</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9155,6 +9560,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91171450</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9256,6 +9666,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811589</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9357,6 +9772,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879353</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9458,6 +9878,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811547</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9559,6 +9984,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811611</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9661,6 +10091,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120489103</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9763,6 +10198,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811532</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9870,6 +10310,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811525</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9972,6 +10417,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128811563</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10082,6 +10532,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101202671</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10192,6 +10647,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102002236</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10307,6 +10767,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132810978</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10426,6 +10891,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110471525</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10536,6 +11006,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843531</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10637,6 +11112,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314799</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10738,6 +11218,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812222</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10848,6 +11333,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076337</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10964,6 +11454,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94203666</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11074,6 +11569,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102183065</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11176,6 +11676,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110471527</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11295,6 +11800,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109766771</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11409,6 +11919,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94700392</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11520,6 +12035,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94700369</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11617,6 +12137,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126409409</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11715,6 +12240,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93111061</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11829,6 +12359,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116060267</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11930,6 +12465,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142045</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12031,6 +12571,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812133</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12137,6 +12682,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104738</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12238,6 +12788,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104810</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12344,6 +12899,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104825</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12450,6 +13010,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104897</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12556,6 +13121,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105067</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12657,6 +13227,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105882</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12763,6 +13338,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106005</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12864,6 +13444,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106032</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12965,6 +13550,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106037</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13071,6 +13661,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106046</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13177,6 +13772,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106056</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13278,6 +13878,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142015</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13379,6 +13984,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691374</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13480,6 +14090,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691590</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13581,6 +14196,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795014</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13682,6 +14302,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691518</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13783,6 +14408,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691581</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13884,6 +14514,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794852</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13985,6 +14620,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794993</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14086,6 +14726,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833675</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14187,6 +14832,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795127</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14293,6 +14943,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104924</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14394,6 +15049,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105879</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14495,6 +15155,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795993</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14596,6 +15261,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812110</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14702,6 +15372,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105878</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14807,6 +15482,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833660</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14917,6 +15597,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130105470</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15023,6 +15708,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879395</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15124,6 +15814,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781747</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15225,6 +15920,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075088</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15326,6 +16026,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075094</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15432,6 +16137,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076308</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15538,6 +16248,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130076319</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15639,6 +16354,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104631</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15745,6 +16465,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130104720</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15851,6 +16576,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130106064</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15952,6 +16682,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130141666</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16053,6 +16788,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130141670</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16154,6 +16894,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112561926</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16255,6 +17000,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691118</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16356,6 +17106,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721909</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16457,6 +17212,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722425</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16558,6 +17318,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691107</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16659,6 +17424,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794552</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16760,6 +17530,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722038</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16861,6 +17636,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795135</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16962,6 +17742,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794688</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17063,6 +17848,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794716</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17164,6 +17954,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794764</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17265,6 +18060,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721818</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17366,6 +18166,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722064</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17467,6 +18272,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722427</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17568,6 +18378,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722437</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17669,6 +18484,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794677</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17770,6 +18590,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794779</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17871,6 +18696,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794834</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17972,6 +18802,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794930</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18073,6 +18908,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794727</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18174,6 +19014,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722083</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18275,6 +19120,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722278</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18376,6 +19226,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722323</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18477,6 +19332,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794788</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18578,6 +19438,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795142</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18679,6 +19544,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721859</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18780,6 +19650,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722195</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18881,6 +19756,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722480</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -18982,6 +19862,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722486</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19083,6 +19968,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722491</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19184,6 +20074,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722612</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19285,6 +20180,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795954</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19386,6 +20286,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795978</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19487,6 +20392,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795985</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19588,6 +20498,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112561936</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19689,6 +20604,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722246</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19790,6 +20710,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722449</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19891,6 +20816,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794748</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20016,6 +20946,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127873389</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20125,6 +21060,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93870894</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20230,6 +21170,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721895</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20335,6 +21280,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794811</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20440,6 +21390,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131034825</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20541,6 +21496,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130074964</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20642,6 +21602,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130075077</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20743,6 +21708,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130141638</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20844,6 +21814,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130141648</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20945,6 +21920,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722505</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21046,6 +22026,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721737</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21147,6 +22132,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721793</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21248,6 +22238,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722499</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21349,6 +22344,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128795245</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21450,6 +22450,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120489091</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21551,6 +22556,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721612</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21652,6 +22662,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721657</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21753,6 +22768,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721668</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21854,6 +22874,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721681</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21955,6 +22980,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128721801</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22069,6 +23099,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123884335</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22170,6 +23205,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722827</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22275,6 +23315,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132428269</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22377,6 +23422,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125871519</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22484,6 +23534,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81129214</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22591,6 +23646,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89283948</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22693,6 +23753,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120489147</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22800,6 +23865,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794373</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22907,6 +23977,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128794388</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23008,6 +24083,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833040</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23111,6 +24191,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120026935</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23226,6 +24311,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132429924</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23328,6 +24418,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134928863</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23434,6 +24529,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781675</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23535,6 +24635,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142063</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23636,6 +24741,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142101</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23737,6 +24847,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97085757</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23843,6 +24958,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781666</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -23949,6 +25069,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142090</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24052,6 +25177,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142078</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24153,6 +25283,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89283686</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24259,6 +25394,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89283779</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24365,6 +25505,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89283787</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24466,6 +25611,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781692</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24567,6 +25717,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114781701</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24668,6 +25823,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175454</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24769,6 +25929,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175465</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24870,6 +26035,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175481</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -24976,6 +26146,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175516</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25082,6 +26257,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175605</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25183,6 +26363,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112691613</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25284,6 +26469,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833238</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25385,6 +26575,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833406</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25486,6 +26681,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833420</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25587,6 +26787,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92183797</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25688,6 +26893,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833200</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25789,6 +26999,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142343</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25890,6 +27105,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175882</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -25991,6 +27211,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812144</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26092,6 +27317,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833270</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26193,6 +27423,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833510</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26307,6 +27542,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121384572</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26412,6 +27652,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128833347</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26517,6 +27762,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175591</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26623,6 +27873,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130175582</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26724,6 +27979,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722809</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26829,6 +28089,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89283803</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26930,6 +28195,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722624</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27035,6 +28305,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128812203</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27136,6 +28411,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130141692</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27242,6 +28522,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/13544750</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27343,6 +28628,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142345</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27444,6 +28734,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142349</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27545,6 +28840,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722658</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27646,6 +28946,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722513</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27747,6 +29052,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722666</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27848,6 +29158,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122757052</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -27949,6 +29264,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142355</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28050,6 +29370,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112946706</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28151,6 +29476,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120489098</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28252,6 +29582,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128722662</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -28366,6 +29701,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131936827</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -28471,6 +29811,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121836761</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -28576,6 +29921,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132429104</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -28681,6 +30031,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96879439</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -28793,6 +30148,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124537248</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -28908,6 +30268,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100206959</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29009,6 +30374,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142142</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29115,6 +30485,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142269</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -29216,6 +30591,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142146</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -29322,6 +30702,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142277</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -29428,6 +30813,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142295</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -29534,6 +30924,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142129</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -29643,6 +31038,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122279615</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -29748,6 +31148,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142285</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -29849,8 +31254,296 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130142299</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>135152950</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>135386753</v>
       </c>
       <c r="B13" t="n">
-        <v>107789</v>
+        <v>107844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>134928863</v>
       </c>
       <c r="B219" t="n">
-        <v>106324</v>
+        <v>106379</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1916,7 +1916,7 @@
         <v>135386753</v>
       </c>
       <c r="B13" t="n">
-        <v>107844</v>
+        <v>107871</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1802,7 +1802,7 @@
         <v>135386753</v>
       </c>
       <c r="B12" t="n">
-        <v>107876</v>
+        <v>107878</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -10664,7 +10664,7 @@
         <v>136050898</v>
       </c>
       <c r="B93" t="n">
-        <v>96723</v>
+        <v>96724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -10664,7 +10664,7 @@
         <v>136050898</v>
       </c>
       <c r="B93" t="n">
-        <v>96724</v>
+        <v>96725</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>136239010</v>
       </c>
       <c r="B101" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>136050860</v>
       </c>
       <c r="B220" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>136239010</v>
       </c>
       <c r="B101" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>136050860</v>
       </c>
       <c r="B220" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>136239010</v>
       </c>
       <c r="B101" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>136050860</v>
       </c>
       <c r="B220" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
+++ b/artfynd/Norrbytorps naturreservat söder artfynd.xlsx
@@ -1918,7 +1918,7 @@
         <v>136261248</v>
       </c>
       <c r="B13" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>136050898</v>
       </c>
       <c r="B95" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>136239010</v>
       </c>
       <c r="B101" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>136050860</v>
       </c>
       <c r="B220" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
